--- a/artfynd/A 62678-2025 artfynd.xlsx
+++ b/artfynd/A 62678-2025 artfynd.xlsx
@@ -906,7 +906,7 @@
         <v>131239963</v>
       </c>
       <c r="B4" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 62678-2025 artfynd.xlsx
+++ b/artfynd/A 62678-2025 artfynd.xlsx
@@ -906,7 +906,7 @@
         <v>131239963</v>
       </c>
       <c r="B4" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 62678-2025 artfynd.xlsx
+++ b/artfynd/A 62678-2025 artfynd.xlsx
@@ -906,7 +906,7 @@
         <v>131239963</v>
       </c>
       <c r="B4" t="n">
-        <v>57884</v>
+        <v>57885</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 62678-2025 artfynd.xlsx
+++ b/artfynd/A 62678-2025 artfynd.xlsx
@@ -906,7 +906,7 @@
         <v>131239963</v>
       </c>
       <c r="B4" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 62678-2025 artfynd.xlsx
+++ b/artfynd/A 62678-2025 artfynd.xlsx
@@ -906,7 +906,7 @@
         <v>131239963</v>
       </c>
       <c r="B4" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 62678-2025 artfynd.xlsx
+++ b/artfynd/A 62678-2025 artfynd.xlsx
@@ -906,7 +906,7 @@
         <v>131239963</v>
       </c>
       <c r="B4" t="n">
-        <v>57889</v>
+        <v>57895</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 62678-2025 artfynd.xlsx
+++ b/artfynd/A 62678-2025 artfynd.xlsx
@@ -906,7 +906,7 @@
         <v>131239963</v>
       </c>
       <c r="B4" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 62678-2025 artfynd.xlsx
+++ b/artfynd/A 62678-2025 artfynd.xlsx
@@ -906,7 +906,7 @@
         <v>131239963</v>
       </c>
       <c r="B4" t="n">
-        <v>57896</v>
+        <v>57899</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 62678-2025 artfynd.xlsx
+++ b/artfynd/A 62678-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113905311</v>
+        <v>131239963</v>
       </c>
       <c r="B2" t="n">
-        <v>57284</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102977</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -717,7 +712,7 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -757,12 +752,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-01-05</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-01-05</t>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Trummar flitigt.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,37 +789,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113905303</v>
+        <v>113905311</v>
       </c>
       <c r="B3" t="n">
-        <v>57414</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57947</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>102977</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -903,10 +898,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131239963</v>
+        <v>113905303</v>
       </c>
       <c r="B4" t="n">
-        <v>57899</v>
+        <v>58114</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -914,21 +909,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -940,7 +935,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -980,17 +975,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2024-01-05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Trummar flitigt.</t>
+          <t>2024-01-05</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 62678-2025 artfynd.xlsx
+++ b/artfynd/A 62678-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -786,6 +791,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131239963</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -895,6 +905,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113905311</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1004,8 +1019,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113905303</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>